--- a/frontend/tests/e2e/fixtures/p12-pro6004-compras.xlsx
+++ b/frontend/tests/e2e/fixtures/p12-pro6004-compras.xlsx
@@ -5220,13 +5220,21 @@
       <c r="G5" s="15" t="inlineStr"/>
       <c r="H5" s="15" t="inlineStr"/>
       <c r="I5" s="15" t="inlineStr"/>
-      <c r="J5" s="15" t="inlineStr"/>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <t>20.00</t>
+        </is>
+      </c>
       <c r="K5" s="15" t="inlineStr"/>
       <c r="L5" s="15" t="inlineStr"/>
       <c r="M5" s="15" t="inlineStr"/>
       <c r="N5" s="15" t="inlineStr"/>
       <c r="O5" s="15" t="inlineStr"/>
-      <c r="P5" s="15" t="inlineStr"/>
+      <c r="P5" s="15" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
       <c r="Q5" s="15" t="inlineStr"/>
       <c r="R5" s="15" t="inlineStr"/>
       <c r="S5" s="15" t="inlineStr"/>
@@ -5280,7 +5288,7 @@
       </c>
       <c r="AF5" s="15" t="inlineStr">
         <is>
-          <t>OT 385 del taller (NuveraPro, 29-10-2025), págs. 1, 6 y 7</t>
+          <t>OT 385 del taller (NuveraPro, 29-10-2025), págs. 1, 6 y 7; peso y área máxima: ficha de vidrio del taller de ensayo</t>
         </is>
       </c>
     </row>

--- a/frontend/tests/e2e/fixtures/p12-pro6004-compras.xlsx
+++ b/frontend/tests/e2e/fixtures/p12-pro6004-compras.xlsx
@@ -13,7 +13,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Vidrios" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Reglas de vidrio" sheetId="9" state="visible" r:id="rId9"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Herrajes" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Precios de costo" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Fijaciones" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Precios de costo" sheetId="12" state="visible" r:id="rId12"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sistemas'!$A$4:$AJ$24</definedName>
@@ -26,7 +27,8 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="7" hidden="1">'Vidrios'!$A$4:$AF$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="8" hidden="1">'Reglas de vidrio'!$A$4:$I$24</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="9" hidden="1">'Herrajes'!$A$4:$R$24</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Precios de costo'!$A$4:$K$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="10" hidden="1">'Fijaciones'!$A$4:$G$24</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11" hidden="1">'Precios de costo'!$A$4:$K$24</definedName>
   </definedNames>
 </workbook>
 </file>
@@ -1969,6 +1971,535 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R24"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="22" customWidth="1" min="1" max="1"/>
+    <col width="22" customWidth="1" min="2" max="2"/>
+    <col width="22" customWidth="1" min="3" max="3"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="22" customWidth="1" min="5" max="5"/>
+    <col width="22" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="26" customWidth="1" min="8" max="8"/>
+    <col width="26" customWidth="1" min="9" max="9"/>
+    <col width="22" customWidth="1" min="10" max="10"/>
+    <col width="22" customWidth="1" min="11" max="11"/>
+    <col width="26" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="22" customWidth="1" min="15" max="15"/>
+    <col width="31" customWidth="1" min="16" max="16"/>
+    <col width="47" customWidth="1" min="17" max="17"/>
+    <col width="22" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Fijaciones</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Completa los datos del proveedor. Vacío = Sin dato. Indica la fuente de cada fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="48" customHeight="1">
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>Código de sistema</t>
+        </is>
+      </c>
+      <c r="B4" s="14" t="inlineStr">
+        <is>
+          <t>SKU</t>
+        </is>
+      </c>
+      <c r="C4" s="14" t="inlineStr">
+        <is>
+          <t>Nombre</t>
+        </is>
+      </c>
+      <c r="D4" s="14" t="inlineStr">
+        <is>
+          <t>SKU de compra</t>
+        </is>
+      </c>
+      <c r="E4" s="14" t="inlineStr">
+        <is>
+          <t>Fabricante</t>
+        </is>
+      </c>
+      <c r="F4" s="14" t="inlineStr">
+        <is>
+          <t>Versión</t>
+        </is>
+      </c>
+      <c r="G4" s="14" t="inlineStr">
+        <is>
+          <t>Fuente</t>
+        </is>
+      </c>
+      <c r="H4" s="14" t="n"/>
+      <c r="I4" s="14" t="n"/>
+      <c r="J4" s="14" t="n"/>
+      <c r="K4" s="14" t="n"/>
+      <c r="L4" s="14" t="n"/>
+      <c r="M4" s="14" t="n"/>
+      <c r="N4" s="14" t="n"/>
+      <c r="O4" s="14" t="n"/>
+      <c r="P4" s="14" t="n"/>
+      <c r="Q4" s="14" t="n"/>
+      <c r="R4" s="14" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="15" t="inlineStr">
+        <is>
+          <t>PRO6004</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="inlineStr">
+        <is>
+          <t>120500051</t>
+        </is>
+      </c>
+      <c r="C5" s="15" t="inlineStr">
+        <is>
+          <t>Tornillo de refuerzo 3,9 × 19 mm</t>
+        </is>
+      </c>
+      <c r="D5" s="15" t="inlineStr">
+        <is>
+          <t>120500051</t>
+        </is>
+      </c>
+      <c r="E5" s="15" t="inlineStr">
+        <is>
+          <t>Proveedor de herrajes del taller</t>
+        </is>
+      </c>
+      <c r="F5" s="15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G5" s="15" t="inlineStr">
+        <is>
+          <t>OT 385 del taller (NuveraPro, 29-10-2025), págs. 1, 6 y 7</t>
+        </is>
+      </c>
+      <c r="H5" s="15" t="n"/>
+      <c r="I5" s="15" t="n"/>
+      <c r="J5" s="15" t="n"/>
+      <c r="K5" s="15" t="n"/>
+      <c r="L5" s="15" t="n"/>
+      <c r="M5" s="15" t="n"/>
+      <c r="N5" s="15" t="n"/>
+      <c r="O5" s="15" t="n"/>
+      <c r="P5" s="15" t="n"/>
+      <c r="Q5" s="15" t="n"/>
+      <c r="R5" s="15" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="15" t="n"/>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
+      <c r="G6" s="15" t="n"/>
+      <c r="H6" s="15" t="n"/>
+      <c r="I6" s="15" t="n"/>
+      <c r="J6" s="15" t="n"/>
+      <c r="K6" s="15" t="n"/>
+      <c r="L6" s="15" t="n"/>
+      <c r="M6" s="15" t="n"/>
+      <c r="N6" s="15" t="n"/>
+      <c r="O6" s="15" t="n"/>
+      <c r="P6" s="15" t="n"/>
+      <c r="Q6" s="15" t="n"/>
+      <c r="R6" s="15" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="15" t="n"/>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
+      <c r="G7" s="15" t="n"/>
+      <c r="H7" s="15" t="n"/>
+      <c r="I7" s="15" t="n"/>
+      <c r="J7" s="15" t="n"/>
+      <c r="K7" s="15" t="n"/>
+      <c r="L7" s="15" t="n"/>
+      <c r="M7" s="15" t="n"/>
+      <c r="N7" s="15" t="n"/>
+      <c r="O7" s="15" t="n"/>
+      <c r="P7" s="15" t="n"/>
+      <c r="Q7" s="15" t="n"/>
+      <c r="R7" s="15" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="15" t="n"/>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
+      <c r="G8" s="15" t="n"/>
+      <c r="H8" s="15" t="n"/>
+      <c r="I8" s="15" t="n"/>
+      <c r="J8" s="15" t="n"/>
+      <c r="K8" s="15" t="n"/>
+      <c r="L8" s="15" t="n"/>
+      <c r="M8" s="15" t="n"/>
+      <c r="N8" s="15" t="n"/>
+      <c r="O8" s="15" t="n"/>
+      <c r="P8" s="15" t="n"/>
+      <c r="Q8" s="15" t="n"/>
+      <c r="R8" s="15" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="15" t="n"/>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
+      <c r="G9" s="15" t="n"/>
+      <c r="H9" s="15" t="n"/>
+      <c r="I9" s="15" t="n"/>
+      <c r="J9" s="15" t="n"/>
+      <c r="K9" s="15" t="n"/>
+      <c r="L9" s="15" t="n"/>
+      <c r="M9" s="15" t="n"/>
+      <c r="N9" s="15" t="n"/>
+      <c r="O9" s="15" t="n"/>
+      <c r="P9" s="15" t="n"/>
+      <c r="Q9" s="15" t="n"/>
+      <c r="R9" s="15" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="n"/>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
+      <c r="G10" s="15" t="n"/>
+      <c r="H10" s="15" t="n"/>
+      <c r="I10" s="15" t="n"/>
+      <c r="J10" s="15" t="n"/>
+      <c r="K10" s="15" t="n"/>
+      <c r="L10" s="15" t="n"/>
+      <c r="M10" s="15" t="n"/>
+      <c r="N10" s="15" t="n"/>
+      <c r="O10" s="15" t="n"/>
+      <c r="P10" s="15" t="n"/>
+      <c r="Q10" s="15" t="n"/>
+      <c r="R10" s="15" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="n"/>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
+      <c r="G11" s="15" t="n"/>
+      <c r="H11" s="15" t="n"/>
+      <c r="I11" s="15" t="n"/>
+      <c r="J11" s="15" t="n"/>
+      <c r="K11" s="15" t="n"/>
+      <c r="L11" s="15" t="n"/>
+      <c r="M11" s="15" t="n"/>
+      <c r="N11" s="15" t="n"/>
+      <c r="O11" s="15" t="n"/>
+      <c r="P11" s="15" t="n"/>
+      <c r="Q11" s="15" t="n"/>
+      <c r="R11" s="15" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="n"/>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
+      <c r="G12" s="15" t="n"/>
+      <c r="H12" s="15" t="n"/>
+      <c r="I12" s="15" t="n"/>
+      <c r="J12" s="15" t="n"/>
+      <c r="K12" s="15" t="n"/>
+      <c r="L12" s="15" t="n"/>
+      <c r="M12" s="15" t="n"/>
+      <c r="N12" s="15" t="n"/>
+      <c r="O12" s="15" t="n"/>
+      <c r="P12" s="15" t="n"/>
+      <c r="Q12" s="15" t="n"/>
+      <c r="R12" s="15" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="15" t="n"/>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
+      <c r="G13" s="15" t="n"/>
+      <c r="H13" s="15" t="n"/>
+      <c r="I13" s="15" t="n"/>
+      <c r="J13" s="15" t="n"/>
+      <c r="K13" s="15" t="n"/>
+      <c r="L13" s="15" t="n"/>
+      <c r="M13" s="15" t="n"/>
+      <c r="N13" s="15" t="n"/>
+      <c r="O13" s="15" t="n"/>
+      <c r="P13" s="15" t="n"/>
+      <c r="Q13" s="15" t="n"/>
+      <c r="R13" s="15" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="15" t="n"/>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
+      <c r="G14" s="15" t="n"/>
+      <c r="H14" s="15" t="n"/>
+      <c r="I14" s="15" t="n"/>
+      <c r="J14" s="15" t="n"/>
+      <c r="K14" s="15" t="n"/>
+      <c r="L14" s="15" t="n"/>
+      <c r="M14" s="15" t="n"/>
+      <c r="N14" s="15" t="n"/>
+      <c r="O14" s="15" t="n"/>
+      <c r="P14" s="15" t="n"/>
+      <c r="Q14" s="15" t="n"/>
+      <c r="R14" s="15" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="n"/>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
+      <c r="G15" s="15" t="n"/>
+      <c r="H15" s="15" t="n"/>
+      <c r="I15" s="15" t="n"/>
+      <c r="J15" s="15" t="n"/>
+      <c r="K15" s="15" t="n"/>
+      <c r="L15" s="15" t="n"/>
+      <c r="M15" s="15" t="n"/>
+      <c r="N15" s="15" t="n"/>
+      <c r="O15" s="15" t="n"/>
+      <c r="P15" s="15" t="n"/>
+      <c r="Q15" s="15" t="n"/>
+      <c r="R15" s="15" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="15" t="n"/>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
+      <c r="G16" s="15" t="n"/>
+      <c r="H16" s="15" t="n"/>
+      <c r="I16" s="15" t="n"/>
+      <c r="J16" s="15" t="n"/>
+      <c r="K16" s="15" t="n"/>
+      <c r="L16" s="15" t="n"/>
+      <c r="M16" s="15" t="n"/>
+      <c r="N16" s="15" t="n"/>
+      <c r="O16" s="15" t="n"/>
+      <c r="P16" s="15" t="n"/>
+      <c r="Q16" s="15" t="n"/>
+      <c r="R16" s="15" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="15" t="n"/>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
+      <c r="G17" s="15" t="n"/>
+      <c r="H17" s="15" t="n"/>
+      <c r="I17" s="15" t="n"/>
+      <c r="J17" s="15" t="n"/>
+      <c r="K17" s="15" t="n"/>
+      <c r="L17" s="15" t="n"/>
+      <c r="M17" s="15" t="n"/>
+      <c r="N17" s="15" t="n"/>
+      <c r="O17" s="15" t="n"/>
+      <c r="P17" s="15" t="n"/>
+      <c r="Q17" s="15" t="n"/>
+      <c r="R17" s="15" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="15" t="n"/>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
+      <c r="G18" s="15" t="n"/>
+      <c r="H18" s="15" t="n"/>
+      <c r="I18" s="15" t="n"/>
+      <c r="J18" s="15" t="n"/>
+      <c r="K18" s="15" t="n"/>
+      <c r="L18" s="15" t="n"/>
+      <c r="M18" s="15" t="n"/>
+      <c r="N18" s="15" t="n"/>
+      <c r="O18" s="15" t="n"/>
+      <c r="P18" s="15" t="n"/>
+      <c r="Q18" s="15" t="n"/>
+      <c r="R18" s="15" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="15" t="n"/>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
+      <c r="G19" s="15" t="n"/>
+      <c r="H19" s="15" t="n"/>
+      <c r="I19" s="15" t="n"/>
+      <c r="J19" s="15" t="n"/>
+      <c r="K19" s="15" t="n"/>
+      <c r="L19" s="15" t="n"/>
+      <c r="M19" s="15" t="n"/>
+      <c r="N19" s="15" t="n"/>
+      <c r="O19" s="15" t="n"/>
+      <c r="P19" s="15" t="n"/>
+      <c r="Q19" s="15" t="n"/>
+      <c r="R19" s="15" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="15" t="n"/>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+      <c r="G20" s="15" t="n"/>
+      <c r="H20" s="15" t="n"/>
+      <c r="I20" s="15" t="n"/>
+      <c r="J20" s="15" t="n"/>
+      <c r="K20" s="15" t="n"/>
+      <c r="L20" s="15" t="n"/>
+      <c r="M20" s="15" t="n"/>
+      <c r="N20" s="15" t="n"/>
+      <c r="O20" s="15" t="n"/>
+      <c r="P20" s="15" t="n"/>
+      <c r="Q20" s="15" t="n"/>
+      <c r="R20" s="15" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="15" t="n"/>
+      <c r="B21" s="15" t="n"/>
+      <c r="C21" s="15" t="n"/>
+      <c r="D21" s="15" t="n"/>
+      <c r="E21" s="15" t="n"/>
+      <c r="F21" s="15" t="n"/>
+      <c r="G21" s="15" t="n"/>
+      <c r="H21" s="15" t="n"/>
+      <c r="I21" s="15" t="n"/>
+      <c r="J21" s="15" t="n"/>
+      <c r="K21" s="15" t="n"/>
+      <c r="L21" s="15" t="n"/>
+      <c r="M21" s="15" t="n"/>
+      <c r="N21" s="15" t="n"/>
+      <c r="O21" s="15" t="n"/>
+      <c r="P21" s="15" t="n"/>
+      <c r="Q21" s="15" t="n"/>
+      <c r="R21" s="15" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="n"/>
+      <c r="B22" s="15" t="n"/>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="15" t="n"/>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="15" t="n"/>
+      <c r="G22" s="15" t="n"/>
+      <c r="H22" s="15" t="n"/>
+      <c r="I22" s="15" t="n"/>
+      <c r="J22" s="15" t="n"/>
+      <c r="K22" s="15" t="n"/>
+      <c r="L22" s="15" t="n"/>
+      <c r="M22" s="15" t="n"/>
+      <c r="N22" s="15" t="n"/>
+      <c r="O22" s="15" t="n"/>
+      <c r="P22" s="15" t="n"/>
+      <c r="Q22" s="15" t="n"/>
+      <c r="R22" s="15" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="15" t="n"/>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="15" t="n"/>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="15" t="n"/>
+      <c r="F23" s="15" t="n"/>
+      <c r="G23" s="15" t="n"/>
+      <c r="H23" s="15" t="n"/>
+      <c r="I23" s="15" t="n"/>
+      <c r="J23" s="15" t="n"/>
+      <c r="K23" s="15" t="n"/>
+      <c r="L23" s="15" t="n"/>
+      <c r="M23" s="15" t="n"/>
+      <c r="N23" s="15" t="n"/>
+      <c r="O23" s="15" t="n"/>
+      <c r="P23" s="15" t="n"/>
+      <c r="Q23" s="15" t="n"/>
+      <c r="R23" s="15" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="15" t="n"/>
+      <c r="B24" s="15" t="n"/>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="15" t="n"/>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="15" t="n"/>
+      <c r="G24" s="15" t="n"/>
+      <c r="H24" s="15" t="n"/>
+      <c r="I24" s="15" t="n"/>
+      <c r="J24" s="15" t="n"/>
+      <c r="K24" s="15" t="n"/>
+      <c r="L24" s="15" t="n"/>
+      <c r="M24" s="15" t="n"/>
+      <c r="N24" s="15" t="n"/>
+      <c r="O24" s="15" t="n"/>
+      <c r="P24" s="15" t="n"/>
+      <c r="Q24" s="15" t="n"/>
+      <c r="R24" s="15" t="n"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A4:G24"/>
+  <mergeCells count="2">
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
